--- a/public/templates/forms/A-016-IncidentNotificationEscalationContactList-FORM.xlsx
+++ b/public/templates/forms/A-016-IncidentNotificationEscalationContactList-FORM.xlsx
@@ -3,12 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="29920" windowHeight="20380" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="29920" windowHeight="20380" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Register" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Register!$11:$11</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -16,7 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="11">
     <font>
       <name val="Aptos"/>
@@ -215,7 +220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -283,6 +288,7 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -562,7 +568,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1">
+    <row r="2" ht="34.7" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
           <t>« Replace bracketed fields. This is the call-and-escalation list for the Incident Response Plan; keep it current and verify every contact at least annually. Delete every « » note before publishing. »</t>
@@ -623,7 +629,7 @@
       <c r="G5" s="23" t="n"/>
       <c r="H5" s="22" t="n"/>
     </row>
-    <row r="6" ht="43.5" customHeight="1">
+    <row r="6" ht="50.5" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Classification</t>
@@ -641,7 +647,7 @@
       <c r="G6" s="23" t="n"/>
       <c r="H6" s="22" t="n"/>
     </row>
-    <row r="7" ht="15" customHeight="1">
+    <row r="7" ht="34.7" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Review cadence</t>
@@ -666,14 +672,14 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="27.75" customHeight="1">
+    <row r="10" ht="50.5" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
           <t>« One row per party to be contacted during an incident. Set the call sequence with Escalation Order and use Triggers at Tier to show which severity levels call each party. Include internal roles, vendors (CAD, recording, ISP), the State 911 Board, the Indiana Office of Technology, FBI/CISA, and any managed security service. Names appear in the adopted list, which is why it is Confidential. »</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
           <t>ID</t>
@@ -715,7 +721,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="19.5" customHeight="1">
+    <row r="12" ht="34.7" customHeight="1">
       <c r="A12" s="25" t="inlineStr">
         <is>
           <t>CN-001</t>
@@ -757,7 +763,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="19.5" customHeight="1">
+    <row r="13" ht="34.7" customHeight="1">
       <c r="A13" s="25" t="inlineStr">
         <is>
           <t>CN-002</t>
@@ -799,7 +805,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="19.5" customHeight="1">
+    <row r="14" ht="34.7" customHeight="1">
       <c r="A14" s="25" t="inlineStr">
         <is>
           <t>CN-003</t>
@@ -841,7 +847,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="19.5" customHeight="1">
+    <row r="15" ht="34.7" customHeight="1">
       <c r="A15" s="25" t="inlineStr">
         <is>
           <t>CN-004</t>
@@ -883,7 +889,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="19.5" customHeight="1">
+    <row r="16" ht="34.7" customHeight="1">
       <c r="A16" s="25" t="inlineStr">
         <is>
           <t>CN-005</t>
@@ -991,7 +997,6 @@
       <c r="B24" s="26" t="n"/>
       <c r="C24" s="13">
         <f>COUNTA(A12:A21)</f>
-        <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
@@ -1003,7 +1008,6 @@
       <c r="B25" s="26" t="n"/>
       <c r="C25" s="13">
         <f>COUNTIFS(A12:A21,"&lt;&gt;",H12:H21,"&gt;="&amp;(TODAY()-365))</f>
-        <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
@@ -1015,7 +1019,6 @@
       <c r="B26" s="26" t="n"/>
       <c r="C26" s="13">
         <f>COUNTIFS(A12:A21,"&lt;&gt;",H12:H21,"&lt;"&amp;(TODAY()-365))</f>
-        <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
@@ -1027,7 +1030,6 @@
       <c r="B27" s="26" t="n"/>
       <c r="C27" s="13">
         <f>COUNTIFS(A12:A21,"&lt;&gt;",H12:H21,"")</f>
-        <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
@@ -1191,10 +1193,10 @@
       <c r="F45" s="12" t="n"/>
       <c r="G45" s="12" t="n"/>
     </row>
-    <row r="47" ht="30" customHeight="1">
+    <row r="47" ht="82.2" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Drafter's note (internal, delete before publishing): Inventory/Register form, build-order #67 (A-016). Reshaped from the generic register into an incident call-and-escalation roster: the Status / Last-Reviewed / Next-Review columns were replaced with contact, tier-trigger, escalation-order, and last-verified columns, and the status COUNTIF summary was swapped for a verification-currency check keyed to the annual-update requirement. Consolidates the notification-matrix and external-contact-list functions the source spec listed separately. Classification Confidential / CJIS per the Tracker. Maintained separately from the Incident Response Plan for operational use.</t>
+          <t>Drafter's note (internal, delete before publishing): Inventory/Register form, build-order #67. Reshaped from the generic register into an incident call-and-escalation roster: the Status / Last-Reviewed / Next-Review columns were replaced with contact, tier-trigger, escalation-order, and last-verified columns, and the status COUNTIF summary was swapped for a verification-currency check keyed to the annual-update requirement. Consolidates the notification-matrix and external-contact-list functions the source spec listed separately. Classification Confidential / CJIS per the Tracker. Maintained separately from the Incident Response Plan for operational use.</t>
         </is>
       </c>
     </row>
@@ -1231,14 +1233,18 @@
     <mergeCell ref="C4:H4"/>
     <mergeCell ref="A31:H31"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="E12:E21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Status" prompt="Select a status" type="list">
       <formula1>"Active,Under Review,Retired,Decommissioned"</formula1>
       <formula2>0</formula2>
     </dataValidation>
+    <dataValidation sqref="F12:F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Escalation Order" prompt="Select a value" type="list">
+      <formula1>"1,2,3,4,5,6,7,8"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -1246,7 +1252,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
@@ -1264,14 +1270,14 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="43.5" customHeight="1">
+    <row r="2" ht="50.5" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>How to use this template: list every party to call during an incident, one row each. Use Escalation Order for the call sequence and Triggers at Tier to show which severity levels call each party. Verify every contact at least annually. Replace every [BRACKETED] field and delete every « » note before publishing.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="29.75" customHeight="1">
+    <row r="3" ht="34.7" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Placeholder key:  [BRACKETED] = fill in   ·   « » = guidance to delete.  Classification, Source Authority, signatures and revision history live on the Register tab.</t>
@@ -1329,7 +1335,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
+    <row r="8" ht="34.7" customHeight="1">
       <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Contact (Party &amp; Role)</t>
@@ -1373,7 +1379,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
+    <row r="10" ht="34.7" customHeight="1">
       <c r="A10" s="17" t="inlineStr">
         <is>
           <t>Alternate Contact</t>
@@ -1395,7 +1401,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Triggers at Tier</t>
@@ -1439,7 +1445,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
+    <row r="13" ht="34.7" customHeight="1">
       <c r="A13" s="17" t="inlineStr">
         <is>
           <t>Availability</t>
@@ -1477,13 +1483,11 @@
           <t>Required</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="29.75" customHeight="1">
+      <c r="D14" s="27">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="15" ht="34.7" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
           <t>« Summary on the Register tab counts total contacts and flags those verified within the last year, overdue for verification, or awaiting a first verification. »</t>
@@ -1577,6 +1581,6 @@
     <mergeCell ref="B20:D20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>